--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894385</v>
       </c>
       <c r="B2" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136894735</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136895532</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894385</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136894735</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136895532</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Kvarnbäcken, Dlr</t>
@@ -831,11 +827,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Kvarnbäcken, Dlr</t>
@@ -957,16 +949,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sågtjärnen, Sågtjärnen, Dlr</t>

--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894385</v>
       </c>
       <c r="B2" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136894735</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136895532</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894385</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136894735</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136895532</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39527-2026 artfynd.xlsx
+++ b/artfynd/A 39527-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894385</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136894735</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136895532</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
